--- a/legal_rag_tester/questions.xlsx
+++ b/legal_rag_tester/questions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -137,252 +137,6 @@
   </si>
   <si>
     <t>Если при подаче заявки в АЗ Казахинвест указать собственные средства, то сумма инвестиций в размере 4 000 000 000 тенге, указанная в бизнес плане сразу должно быть внесено в при подачи заявки? А если мы укажем при подаче заявки заемные средства, то этот договор мы можем после подачи заявки расторгнуть и расходы по распределению инвестиционных затрат осуществлять за счет собственных средств по мере поступления этих средств с инвестора с Китая, в этот случае какой договор с инвестором заключить нужно, или инвестора включить как участника ТОО будет достаточно?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0029</t>
-  </si>
-  <si>
-    <t>Ученики 6 класса без разрешения учителя перед началом урока зашли в кабинет. Учитель пришёл и вытащил рюкзаки в коридор. Когда ученики зашли в кабинет на урок, то посмотрев телефоны предъявили учителю что у телефонов треснули стекла. Но когда пришла классный руководитель то выяснилось что у телефонов были небольшие трещины. Но родительница одного из учеников заявила чтобы учитель возместил ущерб. Кто прав?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0031</t>
-  </si>
-  <si>
-    <t>Мама хочет оформить дарение своей квартиры на дочь и зятя (50/50). Возможна ли данная процедура и будет ли взиматься налог с зятя как не с близкого родственника в размере 10% его доли. Если нет, то какие налоги необходимо будет оплатить?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0032</t>
-  </si>
-  <si>
-    <t>На, многократные, повторные, наши Запросы, Потребителей - на электронную почту, на имя - Генерального Директора Головного ТОО! О завершении - Гарантийного Ремонта, нашего Автомобиля! Не было - ответов, уже. несколько лет! Как, мы, Вправе - Наказать Генерального Директора Головного ТОО - За неуважение к нам - Потребителям? Игнорирование наших - Запросов! А, главное - Не издание Приказа О Завершении Гарантийного Ремонта, нашего - Автомобиля! Для ТОО - Исполнителя! На какие Законы РК, нам, следует ссылаться? Кроме Закона РК - О Защите Прав Потребителей! Куда, нам, следует направить - досудебную претензию - на, его, домашний адрес? За нанесение - Морального вреда и вреда здоровью нам? Или, можно - в офис Головного ТОО? Есть ли - Ограничения в сумме взыскания - За Моральный Вред Так как, ранее, нам, Незаконно, было - Отказано! В Добровольной Уплате Неустойки - За просрочку срока - Гарантийного Ремонта, нашего - Автомобиля! С Уважением, Рафхат и Болат Абдреимовы.</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0034</t>
-  </si>
-  <si>
-    <t>Здравствуйте.Меня зовут Валентина. Место проживания- Греция. Я нахожусь на стадии оформления опекунства над моей мамой, имеющей казахстанское гражданство, вид на жительство в Греции и проживающей со мной в одном доме, по причине тяжёлого психического недуга (Альцгеймера), полной недееспособности, подтверждённой решением суда (в Греции) о временном опекунстве (действующем до окончательного решения суда). Решение обратиться в суд по вопросу временного (ускоренного) опекунства было принято мной в связи с окончанием срока действия банковской карты Халык БАНК в ноябре 2023г и невозможностью в связи с этим получения пенсии мамы в греческом банкомате. Судебные документы апостилированы. В решении о полномочиях временного опекуна указано лицо (Я) и разрешение оформлять мною доверенность на третье лицо в Казахстане, на предмет общения с банками и различными организациями по вопросу возобновления перечислений пенсии, открытию карт и т.д. Моя цель- возобновление получения маминой заслуженной пенсии и любых других доплат и пособий, установленных Законодательством Казахстана. Вопросы: 1. Какие документы и процедуры необходимы для осуществления этой цели? 2. Нужна ли легализация (судебная или другого вида) на апостелированное судебное решение Греческого Суда? 3. Имеется ли в Казахском кодексе понятие "временное опекунство недееспособного? 4. Имеются ли случаи, когда пенсионер, имеющий Казахстанское гражданство и вид на жительство в Греции, проживающей в Греции, не имеет право получать заслуженную пенсию?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0036</t>
-  </si>
-  <si>
-    <t>Являюсь членом ЖСК, хотим оформить право собственности через ЦОН, но председатель отказывается без объяснения причин, говорит оформлять через нотариус. Правомерны ли действия ЖСК при том, что по договору участия в ЖСК, ЖСК должен подготовить для передачи в гос орган все необходимые для регистрации документы для регистрации права собственности.</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0037</t>
-  </si>
-  <si>
-    <t>Добрый день. В январе 2024 года было открыто исполнительное производство в отношении ТОО, 26 января 2024 года был возврат данного исполнительного производство в связи заключением мирового соглашения между ТОО и банком (составлен график погашения оставшегося суммы кредита). ТОО до сих пор числится в базе должников. В январе 2025 года ЧСИ попытался снять со списка должников, но на его обращение департамент юстиции отказали (причину ЧСИ не огласил). Нами 10 февраля 2025 года было направлено в департамент юстиции г.Алматы обращение на снятие из реестра должников (приложили к данному обращению постановление ЧСИ о возврате исполнительного производства и соглашение меду ТОО и Банком), на что получили отказ в связи тем, что срок исполнения еще не истек (Ответ юстиции: согласно пп. 2, п.6, ст.48 Закона, меры принудительного исполнения подлежат отмене в случаях: истечения срока предъявления исполнительного документа к принудительному исполнению, предусмотренного статьей 11 Закона. Исходя из этого, срок исполнительного листа не прошел, исключить данное производство с Единого реестра должников не представляется возможным). Вопрос: Каким образом мы можем исключение с реестра должников? Возможно ли это? На какие статьи в законодательстве можем ссылаться? Спасибо.</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0038</t>
-  </si>
-  <si>
-    <t>добрый вечер ,я бы хотела спросить вас по поводу займа .Моему сыну 18 лет,учиться в Алматы ,сами живем в городе Кентау Туркестанская область .он живя там взял займ ,вот только что узнала ,написали на вацап ,грубят ,угражают что если он не отдаст начнут судебный процес и тогда они выедут к нам по адресу .брал 20 000 тенге сейчас говорят должен отдать 28 . сумму в своихдокументах не указывают ,так на словах сказали ,скажите пожалуста ,это вообще законно давать детям 18 лет уже займ ! и что я вообще могу сделать по закону ,я пониаюзай мне придется отдать.? займ он взял вписав на сайте acredit.rz свой иин</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0039</t>
-  </si>
-  <si>
-    <t>Доброго Здравия. Хотел бы получить консультацию по пункту 2 статьи 487 Гражданского Кодекса Республики Казахстан, поскольку Комитет атомного и энергетического надзора и контроля произвольно толкует эту норму</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0042</t>
-  </si>
-  <si>
-    <t>Хочу подать на развод, но муж находится в ИВС и я не знаю согласен ли он на развод так как возможности связаться с ним нет. Развод был обговорен с ним давно, но мы не успели подать заявление и сейчас я хочу это сделать сама но не совсем понимаю как это сделать</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0043</t>
-  </si>
-  <si>
-    <t>Два месяца назад я одолжил своему коллеге деньги. Эти деньги были переданы лично. Условия возврата четко не оговаривались, но ожидалось, что долг будет возвращен в разумные сроки. До настоящего времени он не вернул эти средства. Параллельно возникла спорная ситуация с моей заработной платой. В период 13/14 марта я работал и был уверен, что получил оплату за эти смены. Однако недавно одна из сотрудниц написала мне, уточняя, действительно ли я работал в эти дни. Я подтвердил, что работал и, полагая, что оплату получил, сообщил, что всё забрал. Позже я обратился к директору, и она сообщила, что в расходах кассы моей выплаты за эти дни нет, и кассир тоже не подтверждает выдачу. После этого коллега сообщил мне, что якобы «приписал» мне две лишние смены и предложил считать сумму, выданную мне в качестве оплаты, возвратом его долга. Но эти дни я действительно отработал, и не считаю возможным, чтобы моя зарплата покрывала его обязательства. Мне показалось, что он намеренно хотел воспользоваться ситуацией, чтобы не возвращать долг из своих средств. Когда я сказал, что не хочу участвовать в обмане, он лишь ответил: «всё будет нормально», что, на мой взгляд, говорит о его понимании, что деньги — это именно моя зарплата. Позже директор вручила мне конверт с суммой, соответствующей оплате за две смены, но при этом подтвердила, что в расходах кассы этой выплаты нет. Я даже просил посмотреть камеры, но она сказала что уже поздно,(я так понял что записей нет). В итоге я деньги забрал, долг мне еще никто не вернул. Как мне теперь забрать долг? Правильно ли я сделал что взял деньги за эти смены? Если он приписал смены, то как он объяснит расходы кассы.Помогите разобраться!</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0044</t>
-  </si>
-  <si>
-    <t>Добрый День! Просим Вас ответить - нам, на наш вопрос. Вправе ли Потребитель обратиться в суд, с иском - О Взыскании Неустойки, за просрочку срока - Гарантийного Ремонта Автомобиля - С Головного ТОО, Исполнителя? Если, на наши требования - в письме, к - подведомственному ТОО, Исполнителя - О Завершении Гарантийного Ремонта Автомобиля! Исполнитель прислал - нам, Гарантийное письмо от Головного ТОО. В котором, было Запрещение - Исполнителю! В Завершении Гарантийного Ремонта Автомобиля. С Заверением - Что, сама, Компания, самостоятельно, без привлечения - ТОО Исполнителя! Разрешит все вопросы - по Автомобилю и выдаст Автомобиль, его - Владельцу. Но, это - Обязательство, до сих пор, Головным ТОО - не Выполнено! Даже, не приняло мер - на нашу Жалобу! Тогда, когда, Исполнитель - перевез, Незаконно, Автомобиль - на другую территорию и спрятал - от нас, тайно! Тогда, мы, более года - Не знали! Где, наш втомобиль! Кроме того, сейчас, ТОО Исполнителя - Перепродано! А, нас, Умышленно, не уведомляли - об этом! Более того, наши Жалобы и письма в Головное ТОО - Об издании Приказа, для Исполнителя! О Завершении Гарантийного Ремонта Автомобиля были - бесполезными! Вообще - Не ответили, до сих пор! С Уважением, Болат и Рафхат Абдреимовы.</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0045</t>
-  </si>
-  <si>
-    <t>Могу я из своего дома,в отопительный сезон выгнать,семью с маленьким ребёнком,не прописанных в доме и без договора,просто разрешила пожить,теперь они не хотят сьезжать</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0047</t>
-  </si>
-  <si>
-    <t>Вопрос в области страхового права. Прошу Вас, разъяснить мне по нижеследующим вопросам вытекающие из оценки размера вреда, причиненного транспортному средству (по договору добровольного страхования КАСКО). 1) Страховщик (страховая компания) при получении от страхователя (потерпевшего, выгодоприобретателя) заявления о несогласии с размером вреда, причиненного транспортному средству в письменном виде, страховщик в течение скольких дней рассматривает и предоставляет письменный ответ, или страховщик не обязан отвечать на заявления от страхователя (потерпевшего, выгодоприобретателя)? Должен ли Страховщик соблюдать требования Постановления Правления Национального Банка Республики Казахстан от 28 января 2016 года № 14. полностью или частично? Либо руководствуется иными документами? Является ли правомерном озвучивание суммой ущерба в устном виде без предоставлений отчета для ознакомления? 2) Имеет ли право требовать Оценщик страховой компаний от страхователя (потерпевшего, выгодоприобретателя) акта дефектовки официального сервисного центра? В случае разногласий в заменяемых деталей указанные в акте дефектовки должен ли Оценщик страховой компаний пересмотреть свой отчет? Как проверить квалификацию Оценщика страхователю (потерпевшему, выгодоприобретателю), обязан ли или нет Оценщик перед оценкой транспортного средства предоставить для ознакомления страхователю (потерпевшему, выгодоприобретателю) подтверждающее документы в целях подтверждения его личность как оценщика (удостоверение личности, служебное удостоверение, договор оказания услуг по оценке, есть ли квалификация по работе с программным обеспечением для оценки и т.д.) либо достаточно того что он скажет я оценщик? вышеуказанные вопросы очень актуальные на сегодняшний день!</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0051</t>
-  </si>
-  <si>
-    <t>Подруга попросила взять кредит, теперь у нее нет возможности оплачивать, уже второй месяц. Я платила в прошлом месяце сама, в этом месяце такой возможности нет. Что я могу сделать чтоб не портить свою кредитную историю, возможно есть какие то лазейки перекинуть кредит на ее имя и чтоб аресты и штрафные санкции шли на ее счета. А на моей истории это уже не отражалось, так же как я могу обязать ее выплачивать сумму каждый месяц на законном уровне. Заранее благодарю за ответы</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0054</t>
-  </si>
-  <si>
-    <t>Здравствуйте. Год назад я подавала на алименты на супруга, находясь ещё в браке, нам присвоили на двоих несовершеннолетних детей 30 с чем-то тысяч тенге. Так как муж, устроился специально на работу с минимальным доходом. Потом у нас был бракоразводный процесс, но так как дети на момент суда проживали с отцом, то и место жительства детей определили с ним. Алименты подали на меня. После я детей забрала, нашла работу, и не подавала на алименты на супруга. У нас с ним была договорённость устная, о том что он будет помогать. Прошёл год, и его помощь приходится выпрашивать. Меня это не совсем устраивает, так как дети ещё маленькие, младшая ходит в садик, а старшая только пошла в первый класс. Я не могу работать полноценный рабочий день, соответственно мой доход очень низкий для жизни. Хочу снова подать на алименты, чтобы я могла рассчитывать на точную сумму. И могла не бояться. Но если я сейчас подам на алименты, то учитывая его минимальный доход, мне опять присудят всего лишь 30.000. 28 из них будет уходить только на садик для младшей. Ну я знаю что он много работает, он уже съехал с другой девушкой, у которой также есть дети, и он им помогает. При этом он работает автоэлектриком по грузовым машинам, ездит в командировки, то есть весь его доход не отображается официально. А алименты по закону должны выплачиваться из всех доходов, Но я это никак не могу доказать. Как отец он хороший, девочки к нему стремятся, ну я не могу дальше так жить. Я получаю минимум, и у меня он весь уходит чисто на питание. Подскажите пожалуйста, как мне грамотно сделать?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0056</t>
-  </si>
-  <si>
-    <t>При подаче иска важно предоставить доказательства, что вы не знали о кредите, и он не был использован в интересах семьи. Может написать, именно какое доказательство нужно предоставить???</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0057</t>
-  </si>
-  <si>
-    <t>Университет издал указ ректора, о том что справки о болезни без стационарного лечения не являются уважительной причиной пропуска занятий. Можно ли как то повлиять на указ законодательными способами, чтобы его отменить.</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0059</t>
-  </si>
-  <si>
-    <t>Добрый день! В нашу организацию поступило постановление на удержание с заработной платы алиментов на 3 детей. Частный судебный исполнитель указал свой счет для перечисления, хотя счет для алиментов у взыскателя имеется (по нашему запросу чси приложила) и она категорически отказывается поменять этот счет в постановлении. Законно ли это? И второй вопрос: законно ли нам отписаться на постановление на удержание с заработной платы ежеквартально 1 МРП на услуги чси о том, что мы не можем удерживать свыше 50% от заработной платы сотрудника и соответственно не можем исполнить данное постановление?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0060</t>
-  </si>
-  <si>
-    <t>Здравствуйте. В начале 2000-х годов (2006г.) была приобретена квартира. На тот момент я состоял в браке. В 2017г. брак был расторгнут. Доля супруги при разводе не была выделена. Также имеются двое детей 17 и 20 лет. На них тоже в момент развода доля не была выделена. Квартира на данный момент в залоге у банка (ипотека). Возможно-ли сейчас, в 2025г., выделить доли супруги и детей? Не пропущен-ли исковой срок для этого? Заранее спасибо за ответ.</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0061</t>
-  </si>
-  <si>
-    <t>Здравствуйте, я как собственник супермаркета, в котором в спец.отделе размещены информационные материалы, в виде плакатов, стендов алкогольной продукции. Согласно Закона о рекламе, реклама алкогольных напитков запрещена. Вопрос где и в каких местах (запрещена, разрешена)? Кто курирует вопросы внутренней рекламы? Кто может штрафовать или выносить предупреждения и имеют ли право? В архитектуру города в наш адрес не раз поступают обращения, якобы мы размещаем запрещенную рекламу и просят нас оштрафовать. Насколько я знаю архитектура только по наружной рекламе, а внутренняя .... с кем согласовывать, кто проверяет или ведет мониторинг. Заранее благодарю за предоставленный ответ.</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0063</t>
-  </si>
-  <si>
-    <t>Добрый День! Просим Вас ответить - нам, на наш вопрос. Вправе ли Потребитель обратиться в суд, с иском - О Взыскании Неустойки, за просрочку срока - Гарантийного Ремонта Автомобиля - С Головного ТОО, Исполнителя? Если, на наши, Законные, требования - в письме, к ТОО Исполнителя - О Завершении Гарантийного Ремонта Автомобиля! Исполнитель прислал - нам, Гарантийное письмо от Головного ТОО. В котором, было Запрещение - Исполнителю! В Завершении Гарантийного Ремонта Автомобиля. С Заверением - Что, сама, Компания, самостоятельно, без привлечения - ТОО Исполнителя! Разрешит все вопросы - по Автомобилю и выдаст Автомобиль, его - Владельцу. Но, это - Обязательство, до сих пор, Головным ТОО - не Выполнено! Кроме того, сейчас, ТОО Исполнителя - Перепродано! Нас, Умышленно, не уведомляли - об этом! Более того, тогда, наши Жалобы и письма в Головное ТОО - Об издании Приказа, для Исполнителя! О Завершении Гарантийного Ремонта Автомобиля были - бесполезными! Даже - Не ответили, до сих пор! С Уважением, Болат и Рафхат</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0064</t>
-  </si>
-  <si>
-    <t>Здраствуйте уважаемые юристы. У моего отца гражданство РК (отец умер), у брата гражданство Узб но он свой паспорт потерял 15-16 лет тому назад🤦</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0066</t>
-  </si>
-  <si>
-    <t>Здравствуйте. Взял в рассрочку телевизор в Каспи магазине, ТВ оказался с деффектом изображения(засветы,смещение оттенков). Оформил возврат - продавец якобы сделал экспертизу и конечно же в свою пользу, результаты мне не предоставил, Каспи встал на сторону продавца отказав в возврате средств. Продавец не выходит на связь для возврата ТВ, игнорирует мои обращения в мессенджере, я думал не видит/не слышит/занят, Но обратившись к нему с других номеров (с фейковым вопросом) он сразу отвечает. Сам к нему я визит сделать не могу т.к. он в другом конце страны - между нами 1200км. Помогите подскажите что делать куда обращаться?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0068</t>
-  </si>
-  <si>
-    <t>После развода бывшая жена взяла ипотеку, должен ли бывший супруг оплачивать ипотеку?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0071</t>
-  </si>
-  <si>
-    <t>Здравствуйте. Покупала квартиру где в нотаруесе допустили ошибку непрально забит кадастровый номер,в купле продаже. Как быть?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0073</t>
-  </si>
-  <si>
-    <t>Здравствуйте! Может ли театр отказать в возврате билетов за две недели до мероприятия? Для меня мероприятие более не актуально, и я хочу отказаться от услуги заблаговременно и получить деньги обратно. Театр установил внутреннее правило, что все его билеты невозвратны. Насколько это законно?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0080</t>
-  </si>
-  <si>
-    <t>В настоящее время ГАСК судится с физ лицом касательно самовольной постройки. Физ лицо пытается манипулировать, что квартира с пристройкой в залоге. Банк зная о нарушениях, в том числе пожарно/ газовой сфере настаивает о сохранении постройки. Банк игнорирует риски для других квартир, которые тоже являются залогом в других банках. В этой связи, почему Банк позволяет рисковать залогом других? Чем и какими нормами защищается добропорядочный залогодатель ?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0082</t>
-  </si>
-  <si>
-    <t>Доброго времени суток. Мне 30, девушке 17. Могу ли я вступить с ней в половые связи? Естесственно, обоюдно. Без какких-либо насильственных и противоправных действий с моей с моей стороны. По ст. 122 УК РК вроде можно с 16. Грозит ли мне что-то с юридической стороны? Где-то читал, что до 18 лет могут записать заявление ее родители. Так ли это? Опустим моральную сторону. Заранее спасибо</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0085</t>
-  </si>
-  <si>
-    <t>Здравствуйте! Ситуация такая. Заказали услугу по изготовлению (23.12.2024г) и установки Свай (31.12.2024г). Оплата была на 2 разных ИП. С момента оплаты ни каких услуг не проводится, каждый раз менеджер рассказывает разные истории - «Земля мерзлая, нет нужного размера, оборудование сломалось, на этой неделе все решится, теперь установщик в отпуске и тд. » Как правильно нам поступить в этой ситуации? На какие законы нам опираться, что бы Исполнитель выполнил свои работы, либо вернул деньги. Заранее спасибо за ответ!</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0086</t>
-  </si>
-  <si>
-    <t>Мы являемся ТОО "А" (условно), ТОО "А" является собственником земельного участка с целевым назначением "Строительство и обслуживание подъездной автодороги". Данный земельный участок прилегает к земельному участку ТОО "Б" (условно). Теперь ТОО "А" не может попасть на свой участок для строительства автодороги. Это является частным сервитутом. ТОО "А" направило письмо ТОО "Б" для предоставления частного сервитута для строительства автодороги. Однако согласно законодательства ТОО "Б" предоставила нам Соглашение об установлении частного сервитута земельного участка. В данном Соглашении ТОО "Б" указывает сумму первоначального взноса в размере 50 000 000 млн. тенге и ежемесячного платежа в размер 1 000 000 млн. тенге сроком на три года пользования. ТОО "А" направило письмо в ТОО "Б" об разъяснении указанной суммы. на что ТОО "Б" говорит что на данном земельном участке имеется железнодорожная линия на которую ТОО "Б" понесли затраты. Но согласно сведениям ТОО "А" данная железнодорожная линия не введена в эксплуатацию и отсутствует технический паспорт. ТОО "А" не отказывается оплатить частный сервитут но не такой суммой. Вопрос что делать ТОО "А" в таком случае и как решить вопрос по частному сервитуту. Обращались в суд нам сказали что он является собственником и может указывать любую сумму. Мой телефон 87784964747</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0087</t>
-  </si>
-  <si>
-    <t>Здравствуйте, я с несовершеннолетней дочерью получила в наследство машину, затем оформила право собственности, изначально со свекровью договорились, что я передам по дарению машину. Но т.к есть дочь 3,5 года, решила подарить только свою долю. А долю дочери продать . Но без оплаты. Т.к родственники . Орган опеки дал согласие на сделку. Но потом в будущем у меня не будет проблем с тем, что отсутствует оплата ? Лишь отчуждение доли. Или если укажу небольшую сумму , как поступить?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0088</t>
-  </si>
-  <si>
-    <t>Здравствуйте, я офицер запаса учился в военном институте 4 года и работал по специальности 6 лет, уволился со службы с причиной в связи с отсутствием на работе три и более часов, сейчас я устраиваюсь на работу с вторым дипломом государственное коммунальное предприятие на праве хозяйственного ведения (родильный дом) в хозяйственный отдел инженером по ТБ. Вопрос: 1.Считается ли в стаж работы время когда я учился в военном институте при исчислений должностного оклада 2.Отсутствие на работе три и более часов считается ли по отрицательным мотивом</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0090</t>
-  </si>
-  <si>
-    <t>Здравствуйте. Хотел бы получить небольшую консультацию. Ситуация такая. Родители давно разведены. У меня был отец. Он умер в 2019 году. Он Проживал все это время со своей матерью (моей бабушкой) в квартире. Был там прописан на постоянной основе. Умер в 2019 году, бабушка была жива. Недавно бабушка умерла. Теперь вопрос, имею ли я, как родной сын, долю в квартире (отцовскую часть) ??? Половина квартиры (бабушкина часть) переписана по завещанию на другую внучку. И вот вопрос, имею ли я право на какую то часть от второй половины квартиры?? Я у отца не единственный ребенок. Есть еще один ребенок от другого брака. То есть нас двое официальных.</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0092</t>
-  </si>
-  <si>
-    <t>Добрый день! В разводе 14 лет. Живу в доме приобретено м в браке. После развода муж забрал машину так же совместно приобретеную, в доме разрешил жить , с условием что его часть за дом я должна отдать. Совместный 1 ребёнок, 18 лет , на данный момент студент 1 курса. Алименты официально не платил, подавала на Алименты, но он попросил забрать заявление, думаю если бы официально на нем были Алименты то ему было бы сложно выехать в Россию, уже около 10 лет проживает в России, как мне известно там у него вид на жительство. В этом году хочет приехать продать дом Подскажите , как правильно сделать и как быть. Возможно может быть и есть какие то пути чтоб дом уже по закону можно отсудить на себя или на ребёнка.</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0093</t>
-  </si>
-  <si>
-    <t>Я оставил автомобиль у друга во дворе лишонника прав, он тайно выехал на ней и его арестовали, мне что нибудь грозит?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0094</t>
-  </si>
-  <si>
-    <t>Здравствуйте, подскажите какие меры предпринять, если я плачу алименты каждый месяц но супруга бывшая подала в суд , так как ей мало на ребёнка денег, ребёнку 6 лет , и мне насчитали долгу без всяких данных 2300000 тысяч что мне делать подскажите пожалуйста.</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0096</t>
-  </si>
-  <si>
-    <t>Здравствуйте меня уволили из военной службы 2021 году по отрицательный мотив,я могу восстановиться</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0097</t>
-  </si>
-  <si>
-    <t>Добрый день! Забронировали номер в гостиничном комплексе, сделали предоплату 50 %. Нам выставили удалённый счет на оплату через каспий, мы оплатили. Теперь по возникшим обстоятельствам мы не смогли поехать и соответственно за месяц мы предупредили, что приехать не сможем и попросили, чтобы нам вернули деньги. В ответ нам сказали что вернут деньги с минусом 15 % в течении 5 рабочих дней. Прошло 2 недели, говорят что оформят возврат "завтра". Деньги до сих пор не получили. Скажите пожалуйста как можно вернуть деньги?</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0098</t>
-  </si>
-  <si>
-    <t>Здравствуйте! Мой супруг 1 ноября выезжал с гаража задом и ударил проезжающую машину. Мы живём в небольшом переулке, машин мало, потока нет и именно в этот момент проезжала та машина. На месте вызвали ГАИ, супруг виноват, взяли его страховку. Теперь вот спустя время она звонит и говорит, что сумма ремонта дверей ее машины оценили намного дороже, чем готова выплатить страховая компания. Утверждает, что она работает официально водителем такси, у нее есть ИП, скриншоты, всё отправляет. Суть в том, что сейчас она просит у нас немалую сумму денег за ремонт + за утерю стоимости машины. Если мы не согласны выплатить, то она подаст в суд и выбьет ещё сумму равную ее 1.5 месячному доходу, там вообще большие деньги. Что нам делать? Доводить ли до суда? Можем ли мы на суде потребовать, чтоб она обратилась к более дешёвым специалистам, которые бы отремонтировали ее машину в рамках страховой суммы? Имеет ли она право требовать с нас сумму за утерю внешнего вида машины? А ещё говорит, что сама бывшая судья, все доки готовы, и она на старте подать в суд</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0099</t>
-  </si>
-  <si>
-    <t>Здравствуйте хотела бы узнать. Если я работала не официально и ушла по собственному желанию работодатель обязан выплатить зарплату за все отработанные дни</t>
-  </si>
-  <si>
-    <t>kz_legalrag_0100</t>
-  </si>
-  <si>
-    <t>Бывшая супруга, оформила кредит и указала гарантом меня. Я об этом не слухом не духом. Далее никто меня не ставил в известность и в один прекрасный день ЧСИ накладывает арест. Как мне обжаловать действия. Совместно не проживаем 20 лет.</t>
   </si>
 </sst>
 </file>
@@ -403,7 +157,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="11.0"/>
       <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
@@ -414,9 +168,10 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <u/>
       <sz val="11.0"/>
-      <color rgb="FF434343"/>
-      <name val="Roboto"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
@@ -445,7 +200,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border/>
     <border>
       <left style="thin">
@@ -459,6 +214,34 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
       </bottom>
     </border>
     <border>
@@ -484,6 +267,34 @@
       </top>
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF6F8F9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF6F8F9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF6F8F9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF6F8F9"/>
       </bottom>
     </border>
     <border>
@@ -515,29 +326,41 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -591,7 +414,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:D62" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:D100" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="4">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -819,611 +642,675 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="9"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="9"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="9"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="9"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="4"/>
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="4"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="4"/>
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="4"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="4"/>
+      <c r="A36" s="2"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="7"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="4"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="9"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="4"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="5"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="9"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="4"/>
+      <c r="A42" s="2"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="5"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="9"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="4"/>
+      <c r="A44" s="2"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7"/>
+      <c r="A45" s="6"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="9"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="4"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="5"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="7"/>
+      <c r="A47" s="6"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="9"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="4"/>
+      <c r="A48" s="2"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="5"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7"/>
+      <c r="A49" s="6"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="9"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="4"/>
+      <c r="A50" s="2"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="5"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7"/>
+      <c r="A51" s="6"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="9"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="4"/>
+      <c r="A52" s="2"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="5"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="7"/>
+      <c r="A53" s="6"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="9"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="4"/>
+      <c r="A54" s="2"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="5"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="7"/>
+      <c r="A55" s="6"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="9"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="4"/>
+      <c r="A56" s="2"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="5"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="7"/>
+      <c r="A57" s="6"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="9"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" s="3"/>
-      <c r="D58" s="4"/>
+      <c r="A58" s="2"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="5"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="7"/>
+      <c r="A59" s="6"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="9"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="4"/>
+      <c r="A60" s="2"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="5"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="7"/>
+      <c r="A61" s="6"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="9"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="4"/>
+      <c r="A62" s="2"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="5"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="11"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="11"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="11"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="11"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="11"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="11"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="11"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="11"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="11"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="11"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="11"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="11"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="11"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="11"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="11"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="11"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="11"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="10"/>
+      <c r="D86" s="11"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="11"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="10"/>
+      <c r="D89" s="11"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="10"/>
+      <c r="D90" s="11"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="10"/>
+      <c r="D91" s="11"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="10"/>
+      <c r="D93" s="11"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="11"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="10"/>
+      <c r="D95" s="11"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="10"/>
+      <c r="D97" s="11"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="11"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="10"/>
+      <c r="D99" s="11"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/legal_rag_tester/questions.xlsx
+++ b/legal_rag_tester/questions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
   <si>
     <t>id</t>
   </si>
@@ -137,6 +137,486 @@
   </si>
   <si>
     <t>Если при подаче заявки в АЗ Казахинвест указать собственные средства, то сумма инвестиций в размере 4 000 000 000 тенге, указанная в бизнес плане сразу должно быть внесено в при подачи заявки? А если мы укажем при подаче заявки заемные средства, то этот договор мы можем после подачи заявки расторгнуть и расходы по распределению инвестиционных затрат осуществлять за счет собственных средств по мере поступления этих средств с инвестора с Китая, в этот случае какой договор с инвестором заключить нужно, или инвестора включить как участника ТОО будет достаточно?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0029</t>
+  </si>
+  <si>
+    <t>Ученики 6 класса без разрешения учителя перед началом урока зашли в кабинет. Учитель пришёл и вытащил рюкзаки в коридор. Когда ученики зашли в кабинет на урок, то посмотрев телефоны предъявили учителю что у телефонов треснули стекла. Но когда пришла классный руководитель то выяснилось что у телефонов были небольшие трещины. Но родительница одного из учеников заявила чтобы учитель возместил ущерб. Кто прав?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0031</t>
+  </si>
+  <si>
+    <t>Мама хочет оформить дарение своей квартиры на дочь и зятя (50/50). Возможна ли данная процедура и будет ли взиматься налог с зятя как не с близкого родственника в размере 10% его доли. Если нет, то какие налоги необходимо будет оплатить?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0032</t>
+  </si>
+  <si>
+    <t>На, многократные, повторные, наши Запросы, Потребителей - на электронную почту, на имя - Генерального Директора Головного ТОО! О завершении - Гарантийного Ремонта, нашего Автомобиля! Не было - ответов, уже. несколько лет! Как, мы, Вправе - Наказать Генерального Директора Головного ТОО - За неуважение к нам - Потребителям? Игнорирование наших - Запросов! А, главное - Не издание Приказа О Завершении Гарантийного Ремонта, нашего - Автомобиля! Для ТОО - Исполнителя! На какие Законы РК, нам, следует ссылаться? Кроме Закона РК - О Защите Прав Потребителей! Куда, нам, следует направить - досудебную претензию - на, его, домашний адрес? За нанесение - Морального вреда и вреда здоровью нам? Или, можно - в офис Головного ТОО? Есть ли - Ограничения в сумме взыскания - За Моральный Вред Так как, ранее, нам, Незаконно, было - Отказано! В Добровольной Уплате Неустойки - За просрочку срока - Гарантийного Ремонта, нашего - Автомобиля! С Уважением, Рафхат и Болат Абдреимовы.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0034</t>
+  </si>
+  <si>
+    <t>Здравствуйте.Меня зовут Валентина. Место проживания- Греция. Я нахожусь на стадии оформления опекунства над моей мамой, имеющей казахстанское гражданство, вид на жительство в Греции и проживающей со мной в одном доме, по причине тяжёлого психического недуга (Альцгеймера), полной недееспособности, подтверждённой решением суда (в Греции) о временном опекунстве (действующем до окончательного решения суда). Решение обратиться в суд по вопросу временного (ускоренного) опекунства было принято мной в связи с окончанием срока действия банковской карты Халык БАНК в ноябре 2023г и невозможностью в связи с этим получения пенсии мамы в греческом банкомате. Судебные документы апостилированы. В решении о полномочиях временного опекуна указано лицо (Я) и разрешение оформлять мною доверенность на третье лицо в Казахстане, на предмет общения с банками и различными организациями по вопросу возобновления перечислений пенсии, открытию карт и т.д. Моя цель- возобновление получения маминой заслуженной пенсии и любых других доплат и пособий, установленных Законодательством Казахстана. Вопросы: 1. Какие документы и процедуры необходимы для осуществления этой цели? 2. Нужна ли легализация (судебная или другого вида) на апостелированное судебное решение Греческого Суда? 3. Имеется ли в Казахском кодексе понятие "временное опекунство недееспособного? 4. Имеются ли случаи, когда пенсионер, имеющий Казахстанское гражданство и вид на жительство в Греции, проживающей в Греции, не имеет право получать заслуженную пенсию?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0036</t>
+  </si>
+  <si>
+    <t>Являюсь членом ЖСК, хотим оформить право собственности через ЦОН, но председатель отказывается без объяснения причин, говорит оформлять через нотариус. Правомерны ли действия ЖСК при том, что по договору участия в ЖСК, ЖСК должен подготовить для передачи в гос орган все необходимые для регистрации документы для регистрации права собственности.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0037</t>
+  </si>
+  <si>
+    <t>Добрый день. В январе 2024 года было открыто исполнительное производство в отношении ТОО, 26 января 2024 года был возврат данного исполнительного производство в связи заключением мирового соглашения между ТОО и банком (составлен график погашения оставшегося суммы кредита). ТОО до сих пор числится в базе должников. В январе 2025 года ЧСИ попытался снять со списка должников, но на его обращение департамент юстиции отказали (причину ЧСИ не огласил). Нами 10 февраля 2025 года было направлено в департамент юстиции г.Алматы обращение на снятие из реестра должников (приложили к данному обращению постановление ЧСИ о возврате исполнительного производства и соглашение меду ТОО и Банком), на что получили отказ в связи тем, что срок исполнения еще не истек (Ответ юстиции: согласно пп. 2, п.6, ст.48 Закона, меры принудительного исполнения подлежат отмене в случаях: истечения срока предъявления исполнительного документа к принудительному исполнению, предусмотренного статьей 11 Закона. Исходя из этого, срок исполнительного листа не прошел, исключить данное производство с Единого реестра должников не представляется возможным). Вопрос: Каким образом мы можем исключение с реестра должников? Возможно ли это? На какие статьи в законодательстве можем ссылаться? Спасибо.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0038</t>
+  </si>
+  <si>
+    <t>добрый вечер ,я бы хотела спросить вас по поводу займа .Моему сыну 18 лет,учиться в Алматы ,сами живем в городе Кентау Туркестанская область .он живя там взял займ ,вот только что узнала ,написали на вацап ,грубят ,угражают что если он не отдаст начнут судебный процес и тогда они выедут к нам по адресу .брал 20 000 тенге сейчас говорят должен отдать 28 . сумму в своихдокументах не указывают ,так на словах сказали ,скажите пожалуста ,это вообще законно давать детям 18 лет уже займ ! и что я вообще могу сделать по закону ,я пониаюзай мне придется отдать.? займ он взял вписав на сайте acredit.rz свой иин</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0039</t>
+  </si>
+  <si>
+    <t>Доброго Здравия. Хотел бы получить консультацию по пункту 2 статьи 487 Гражданского Кодекса Республики Казахстан, поскольку Комитет атомного и энергетического надзора и контроля произвольно толкует эту норму</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0042</t>
+  </si>
+  <si>
+    <t>Хочу подать на развод, но муж находится в ИВС и я не знаю согласен ли он на развод так как возможности связаться с ним нет. Развод был обговорен с ним давно, но мы не успели подать заявление и сейчас я хочу это сделать сама но не совсем понимаю как это сделать</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0043</t>
+  </si>
+  <si>
+    <t>Два месяца назад я одолжил своему коллеге деньги. Эти деньги были переданы лично. Условия возврата четко не оговаривались, но ожидалось, что долг будет возвращен в разумные сроки. До настоящего времени он не вернул эти средства. Параллельно возникла спорная ситуация с моей заработной платой. В период 13/14 марта я работал и был уверен, что получил оплату за эти смены. Однако недавно одна из сотрудниц написала мне, уточняя, действительно ли я работал в эти дни. Я подтвердил, что работал и, полагая, что оплату получил, сообщил, что всё забрал. Позже я обратился к директору, и она сообщила, что в расходах кассы моей выплаты за эти дни нет, и кассир тоже не подтверждает выдачу. После этого коллега сообщил мне, что якобы «приписал» мне две лишние смены и предложил считать сумму, выданную мне в качестве оплаты, возвратом его долга. Но эти дни я действительно отработал, и не считаю возможным, чтобы моя зарплата покрывала его обязательства. Мне показалось, что он намеренно хотел воспользоваться ситуацией, чтобы не возвращать долг из своих средств. Когда я сказал, что не хочу участвовать в обмане, он лишь ответил: «всё будет нормально», что, на мой взгляд, говорит о его понимании, что деньги — это именно моя зарплата. Позже директор вручила мне конверт с суммой, соответствующей оплате за две смены, но при этом подтвердила, что в расходах кассы этой выплаты нет. Я даже просил посмотреть камеры, но она сказала что уже поздно,(я так понял что записей нет). В итоге я деньги забрал, долг мне еще никто не вернул. Как мне теперь забрать долг? Правильно ли я сделал что взял деньги за эти смены? Если он приписал смены, то как он объяснит расходы кассы.Помогите разобраться!</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0044</t>
+  </si>
+  <si>
+    <t>Добрый День! Просим Вас ответить - нам, на наш вопрос. Вправе ли Потребитель обратиться в суд, с иском - О Взыскании Неустойки, за просрочку срока - Гарантийного Ремонта Автомобиля - С Головного ТОО, Исполнителя? Если, на наши требования - в письме, к - подведомственному ТОО, Исполнителя - О Завершении Гарантийного Ремонта Автомобиля! Исполнитель прислал - нам, Гарантийное письмо от Головного ТОО. В котором, было Запрещение - Исполнителю! В Завершении Гарантийного Ремонта Автомобиля. С Заверением - Что, сама, Компания, самостоятельно, без привлечения - ТОО Исполнителя! Разрешит все вопросы - по Автомобилю и выдаст Автомобиль, его - Владельцу. Но, это - Обязательство, до сих пор, Головным ТОО - не Выполнено! Даже, не приняло мер - на нашу Жалобу! Тогда, когда, Исполнитель - перевез, Незаконно, Автомобиль - на другую территорию и спрятал - от нас, тайно! Тогда, мы, более года - Не знали! Где, наш втомобиль! Кроме того, сейчас, ТОО Исполнителя - Перепродано! А, нас, Умышленно, не уведомляли - об этом! Более того, наши Жалобы и письма в Головное ТОО - Об издании Приказа, для Исполнителя! О Завершении Гарантийного Ремонта Автомобиля были - бесполезными! Вообще - Не ответили, до сих пор! С Уважением, Болат и Рафхат Абдреимовы.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0045</t>
+  </si>
+  <si>
+    <t>Могу я из своего дома,в отопительный сезон выгнать,семью с маленьким ребёнком,не прописанных в доме и без договора,просто разрешила пожить,теперь они не хотят сьезжать</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0047</t>
+  </si>
+  <si>
+    <t>Вопрос в области страхового права. Прошу Вас, разъяснить мне по нижеследующим вопросам вытекающие из оценки размера вреда, причиненного транспортному средству (по договору добровольного страхования КАСКО). 1) Страховщик (страховая компания) при получении от страхователя (потерпевшего, выгодоприобретателя) заявления о несогласии с размером вреда, причиненного транспортному средству в письменном виде, страховщик в течение скольких дней рассматривает и предоставляет письменный ответ, или страховщик не обязан отвечать на заявления от страхователя (потерпевшего, выгодоприобретателя)? Должен ли Страховщик соблюдать требования Постановления Правления Национального Банка Республики Казахстан от 28 января 2016 года № 14. полностью или частично? Либо руководствуется иными документами? Является ли правомерном озвучивание суммой ущерба в устном виде без предоставлений отчета для ознакомления? 2) Имеет ли право требовать Оценщик страховой компаний от страхователя (потерпевшего, выгодоприобретателя) акта дефектовки официального сервисного центра? В случае разногласий в заменяемых деталей указанные в акте дефектовки должен ли Оценщик страховой компаний пересмотреть свой отчет? Как проверить квалификацию Оценщика страхователю (потерпевшему, выгодоприобретателю), обязан ли или нет Оценщик перед оценкой транспортного средства предоставить для ознакомления страхователю (потерпевшему, выгодоприобретателю) подтверждающее документы в целях подтверждения его личность как оценщика (удостоверение личности, служебное удостоверение, договор оказания услуг по оценке, есть ли квалификация по работе с программным обеспечением для оценки и т.д.) либо достаточно того что он скажет я оценщик? вышеуказанные вопросы очень актуальные на сегодняшний день!</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0051</t>
+  </si>
+  <si>
+    <t>Подруга попросила взять кредит, теперь у нее нет возможности оплачивать, уже второй месяц. Я платила в прошлом месяце сама, в этом месяце такой возможности нет. Что я могу сделать чтоб не портить свою кредитную историю, возможно есть какие то лазейки перекинуть кредит на ее имя и чтоб аресты и штрафные санкции шли на ее счета. А на моей истории это уже не отражалось, так же как я могу обязать ее выплачивать сумму каждый месяц на законном уровне. Заранее благодарю за ответы</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0054</t>
+  </si>
+  <si>
+    <t>Здравствуйте. Год назад я подавала на алименты на супруга, находясь ещё в браке, нам присвоили на двоих несовершеннолетних детей 30 с чем-то тысяч тенге. Так как муж, устроился специально на работу с минимальным доходом. Потом у нас был бракоразводный процесс, но так как дети на момент суда проживали с отцом, то и место жительства детей определили с ним. Алименты подали на меня. После я детей забрала, нашла работу, и не подавала на алименты на супруга. У нас с ним была договорённость устная, о том что он будет помогать. Прошёл год, и его помощь приходится выпрашивать. Меня это не совсем устраивает, так как дети ещё маленькие, младшая ходит в садик, а старшая только пошла в первый класс. Я не могу работать полноценный рабочий день, соответственно мой доход очень низкий для жизни. Хочу снова подать на алименты, чтобы я могла рассчитывать на точную сумму. И могла не бояться. Но если я сейчас подам на алименты, то учитывая его минимальный доход, мне опять присудят всего лишь 30.000. 28 из них будет уходить только на садик для младшей. Ну я знаю что он много работает, он уже съехал с другой девушкой, у которой также есть дети, и он им помогает. При этом он работает автоэлектриком по грузовым машинам, ездит в командировки, то есть весь его доход не отображается официально. А алименты по закону должны выплачиваться из всех доходов, Но я это никак не могу доказать. Как отец он хороший, девочки к нему стремятся, ну я не могу дальше так жить. Я получаю минимум, и у меня он весь уходит чисто на питание. Подскажите пожалуйста, как мне грамотно сделать?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0056</t>
+  </si>
+  <si>
+    <t>При подаче иска важно предоставить доказательства, что вы не знали о кредите, и он не был использован в интересах семьи. Может написать, именно какое доказательство нужно предоставить???</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0057</t>
+  </si>
+  <si>
+    <t>Университет издал указ ректора, о том что справки о болезни без стационарного лечения не являются уважительной причиной пропуска занятий. Можно ли как то повлиять на указ законодательными способами, чтобы его отменить.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0059</t>
+  </si>
+  <si>
+    <t>Добрый день! В нашу организацию поступило постановление на удержание с заработной платы алиментов на 3 детей. Частный судебный исполнитель указал свой счет для перечисления, хотя счет для алиментов у взыскателя имеется (по нашему запросу чси приложила) и она категорически отказывается поменять этот счет в постановлении. Законно ли это? И второй вопрос: законно ли нам отписаться на постановление на удержание с заработной платы ежеквартально 1 МРП на услуги чси о том, что мы не можем удерживать свыше 50% от заработной платы сотрудника и соответственно не можем исполнить данное постановление?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0060</t>
+  </si>
+  <si>
+    <t>Здравствуйте. В начале 2000-х годов (2006г.) была приобретена квартира. На тот момент я состоял в браке. В 2017г. брак был расторгнут. Доля супруги при разводе не была выделена. Также имеются двое детей 17 и 20 лет. На них тоже в момент развода доля не была выделена. Квартира на данный момент в залоге у банка (ипотека). Возможно-ли сейчас, в 2025г., выделить доли супруги и детей? Не пропущен-ли исковой срок для этого? Заранее спасибо за ответ.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0061</t>
+  </si>
+  <si>
+    <t>Здравствуйте, я как собственник супермаркета, в котором в спец.отделе размещены информационные материалы, в виде плакатов, стендов алкогольной продукции. Согласно Закона о рекламе, реклама алкогольных напитков запрещена. Вопрос где и в каких местах (запрещена, разрешена)? Кто курирует вопросы внутренней рекламы? Кто может штрафовать или выносить предупреждения и имеют ли право? В архитектуру города в наш адрес не раз поступают обращения, якобы мы размещаем запрещенную рекламу и просят нас оштрафовать. Насколько я знаю архитектура только по наружной рекламе, а внутренняя .... с кем согласовывать, кто проверяет или ведет мониторинг. Заранее благодарю за предоставленный ответ.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0063</t>
+  </si>
+  <si>
+    <t>Добрый День! Просим Вас ответить - нам, на наш вопрос. Вправе ли Потребитель обратиться в суд, с иском - О Взыскании Неустойки, за просрочку срока - Гарантийного Ремонта Автомобиля - С Головного ТОО, Исполнителя? Если, на наши, Законные, требования - в письме, к ТОО Исполнителя - О Завершении Гарантийного Ремонта Автомобиля! Исполнитель прислал - нам, Гарантийное письмо от Головного ТОО. В котором, было Запрещение - Исполнителю! В Завершении Гарантийного Ремонта Автомобиля. С Заверением - Что, сама, Компания, самостоятельно, без привлечения - ТОО Исполнителя! Разрешит все вопросы - по Автомобилю и выдаст Автомобиль, его - Владельцу. Но, это - Обязательство, до сих пор, Головным ТОО - не Выполнено! Кроме того, сейчас, ТОО Исполнителя - Перепродано! Нас, Умышленно, не уведомляли - об этом! Более того, тогда, наши Жалобы и письма в Головное ТОО - Об издании Приказа, для Исполнителя! О Завершении Гарантийного Ремонта Автомобиля были - бесполезными! Даже - Не ответили, до сих пор! С Уважением, Болат и Рафхат</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0064</t>
+  </si>
+  <si>
+    <t>Здраствуйте уважаемые юристы. У моего отца гражданство РК (отец умер), у брата гражданство Узб но он свой паспорт потерял 15-16 лет тому назад🤦</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0066</t>
+  </si>
+  <si>
+    <t>Здравствуйте. Взял в рассрочку телевизор в Каспи магазине, ТВ оказался с деффектом изображения(засветы,смещение оттенков). Оформил возврат - продавец якобы сделал экспертизу и конечно же в свою пользу, результаты мне не предоставил, Каспи встал на сторону продавца отказав в возврате средств. Продавец не выходит на связь для возврата ТВ, игнорирует мои обращения в мессенджере, я думал не видит/не слышит/занят, Но обратившись к нему с других номеров (с фейковым вопросом) он сразу отвечает. Сам к нему я визит сделать не могу т.к. он в другом конце страны - между нами 1200км. Помогите подскажите что делать куда обращаться?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0068</t>
+  </si>
+  <si>
+    <t>После развода бывшая жена взяла ипотеку, должен ли бывший супруг оплачивать ипотеку?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0071</t>
+  </si>
+  <si>
+    <t>Здравствуйте. Покупала квартиру где в нотаруесе допустили ошибку непрально забит кадастровый номер,в купле продаже. Как быть?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0073</t>
+  </si>
+  <si>
+    <t>Здравствуйте! Может ли театр отказать в возврате билетов за две недели до мероприятия? Для меня мероприятие более не актуально, и я хочу отказаться от услуги заблаговременно и получить деньги обратно. Театр установил внутреннее правило, что все его билеты невозвратны. Насколько это законно?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0080</t>
+  </si>
+  <si>
+    <t>В настоящее время ГАСК судится с физ лицом касательно самовольной постройки. Физ лицо пытается манипулировать, что квартира с пристройкой в залоге. Банк зная о нарушениях, в том числе пожарно/ газовой сфере настаивает о сохранении постройки. Банк игнорирует риски для других квартир, которые тоже являются залогом в других банках. В этой связи, почему Банк позволяет рисковать залогом других? Чем и какими нормами защищается добропорядочный залогодатель ?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0082</t>
+  </si>
+  <si>
+    <t>Доброго времени суток. Мне 30, девушке 17. Могу ли я вступить с ней в половые связи? Естесственно, обоюдно. Без какких-либо насильственных и противоправных действий с моей с моей стороны. По ст. 122 УК РК вроде можно с 16. Грозит ли мне что-то с юридической стороны? Где-то читал, что до 18 лет могут записать заявление ее родители. Так ли это? Опустим моральную сторону. Заранее спасибо</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0085</t>
+  </si>
+  <si>
+    <t>Здравствуйте! Ситуация такая. Заказали услугу по изготовлению (23.12.2024г) и установки Свай (31.12.2024г). Оплата была на 2 разных ИП. С момента оплаты ни каких услуг не проводится, каждый раз менеджер рассказывает разные истории - «Земля мерзлая, нет нужного размера, оборудование сломалось, на этой неделе все решится, теперь установщик в отпуске и тд. » Как правильно нам поступить в этой ситуации? На какие законы нам опираться, что бы Исполнитель выполнил свои работы, либо вернул деньги. Заранее спасибо за ответ!</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0086</t>
+  </si>
+  <si>
+    <t>Мы являемся ТОО "А" (условно), ТОО "А" является собственником земельного участка с целевым назначением "Строительство и обслуживание подъездной автодороги". Данный земельный участок прилегает к земельному участку ТОО "Б" (условно). Теперь ТОО "А" не может попасть на свой участок для строительства автодороги. Это является частным сервитутом. ТОО "А" направило письмо ТОО "Б" для предоставления частного сервитута для строительства автодороги. Однако согласно законодательства ТОО "Б" предоставила нам Соглашение об установлении частного сервитута земельного участка. В данном Соглашении ТОО "Б" указывает сумму первоначального взноса в размере 50 000 000 млн. тенге и ежемесячного платежа в размер 1 000 000 млн. тенге сроком на три года пользования. ТОО "А" направило письмо в ТОО "Б" об разъяснении указанной суммы. на что ТОО "Б" говорит что на данном земельном участке имеется железнодорожная линия на которую ТОО "Б" понесли затраты. Но согласно сведениям ТОО "А" данная железнодорожная линия не введена в эксплуатацию и отсутствует технический паспорт. ТОО "А" не отказывается оплатить частный сервитут но не такой суммой. Вопрос что делать ТОО "А" в таком случае и как решить вопрос по частному сервитуту. Обращались в суд нам сказали что он является собственником и может указывать любую сумму. Мой телефон 87784964747</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0087</t>
+  </si>
+  <si>
+    <t>Здравствуйте, я с несовершеннолетней дочерью получила в наследство машину, затем оформила право собственности, изначально со свекровью договорились, что я передам по дарению машину. Но т.к есть дочь 3,5 года, решила подарить только свою долю. А долю дочери продать . Но без оплаты. Т.к родственники . Орган опеки дал согласие на сделку. Но потом в будущем у меня не будет проблем с тем, что отсутствует оплата ? Лишь отчуждение доли. Или если укажу небольшую сумму , как поступить?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0088</t>
+  </si>
+  <si>
+    <t>Здравствуйте, я офицер запаса учился в военном институте 4 года и работал по специальности 6 лет, уволился со службы с причиной в связи с отсутствием на работе три и более часов, сейчас я устраиваюсь на работу с вторым дипломом государственное коммунальное предприятие на праве хозяйственного ведения (родильный дом) в хозяйственный отдел инженером по ТБ. Вопрос: 1.Считается ли в стаж работы время когда я учился в военном институте при исчислений должностного оклада 2.Отсутствие на работе три и более часов считается ли по отрицательным мотивом</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0090</t>
+  </si>
+  <si>
+    <t>Здравствуйте. Хотел бы получить небольшую консультацию. Ситуация такая. Родители давно разведены. У меня был отец. Он умер в 2019 году. Он Проживал все это время со своей матерью (моей бабушкой) в квартире. Был там прописан на постоянной основе. Умер в 2019 году, бабушка была жива. Недавно бабушка умерла. Теперь вопрос, имею ли я, как родной сын, долю в квартире (отцовскую часть) ??? Половина квартиры (бабушкина часть) переписана по завещанию на другую внучку. И вот вопрос, имею ли я право на какую то часть от второй половины квартиры?? Я у отца не единственный ребенок. Есть еще один ребенок от другого брака. То есть нас двое официальных.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0092</t>
+  </si>
+  <si>
+    <t>Добрый день! В разводе 14 лет. Живу в доме приобретено м в браке. После развода муж забрал машину так же совместно приобретеную, в доме разрешил жить , с условием что его часть за дом я должна отдать. Совместный 1 ребёнок, 18 лет , на данный момент студент 1 курса. Алименты официально не платил, подавала на Алименты, но он попросил забрать заявление, думаю если бы официально на нем были Алименты то ему было бы сложно выехать в Россию, уже около 10 лет проживает в России, как мне известно там у него вид на жительство. В этом году хочет приехать продать дом Подскажите , как правильно сделать и как быть. Возможно может быть и есть какие то пути чтоб дом уже по закону можно отсудить на себя или на ребёнка.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0093</t>
+  </si>
+  <si>
+    <t>Я оставил автомобиль у друга во дворе лишонника прав, он тайно выехал на ней и его арестовали, мне что нибудь грозит?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0094</t>
+  </si>
+  <si>
+    <t>Здравствуйте, подскажите какие меры предпринять, если я плачу алименты каждый месяц но супруга бывшая подала в суд , так как ей мало на ребёнка денег, ребёнку 6 лет , и мне насчитали долгу без всяких данных 2300000 тысяч что мне делать подскажите пожалуйста.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0096</t>
+  </si>
+  <si>
+    <t>Здравствуйте меня уволили из военной службы 2021 году по отрицательный мотив,я могу восстановиться</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0097</t>
+  </si>
+  <si>
+    <t>Добрый день! Забронировали номер в гостиничном комплексе, сделали предоплату 50 %. Нам выставили удалённый счет на оплату через каспий, мы оплатили. Теперь по возникшим обстоятельствам мы не смогли поехать и соответственно за месяц мы предупредили, что приехать не сможем и попросили, чтобы нам вернули деньги. В ответ нам сказали что вернут деньги с минусом 15 % в течении 5 рабочих дней. Прошло 2 недели, говорят что оформят возврат "завтра". Деньги до сих пор не получили. Скажите пожалуйста как можно вернуть деньги?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0098</t>
+  </si>
+  <si>
+    <t>Здравствуйте! Мой супруг 1 ноября выезжал с гаража задом и ударил проезжающую машину. Мы живём в небольшом переулке, машин мало, потока нет и именно в этот момент проезжала та машина. На месте вызвали ГАИ, супруг виноват, взяли его страховку. Теперь вот спустя время она звонит и говорит, что сумма ремонта дверей ее машины оценили намного дороже, чем готова выплатить страховая компания. Утверждает, что она работает официально водителем такси, у нее есть ИП, скриншоты, всё отправляет. Суть в том, что сейчас она просит у нас немалую сумму денег за ремонт + за утерю стоимости машины. Если мы не согласны выплатить, то она подаст в суд и выбьет ещё сумму равную ее 1.5 месячному доходу, там вообще большие деньги. Что нам делать? Доводить ли до суда? Можем ли мы на суде потребовать, чтоб она обратилась к более дешёвым специалистам, которые бы отремонтировали ее машину в рамках страховой суммы? Имеет ли она право требовать с нас сумму за утерю внешнего вида машины? А ещё говорит, что сама бывшая судья, все доки готовы, и она на старте подать в суд</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0099</t>
+  </si>
+  <si>
+    <t>Здравствуйте хотела бы узнать. Если я работала не официально и ушла по собственному желанию работодатель обязан выплатить зарплату за все отработанные дни</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0100</t>
+  </si>
+  <si>
+    <t>Бывшая супруга, оформила кредит и указала гарантом меня. Я об этом не слухом не духом. Далее никто меня не ставил в известность и в один прекрасный день ЧСИ накладывает арест. Как мне обжаловать действия. Совместно не проживаем 20 лет.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0101</t>
+  </si>
+  <si>
+    <t>У меня имеется просроченный кредит. Вопрос: могут ли ЧСИ арестовать арендуемую недвижимость (Я не хозяин квартиры) но прописан, угрожая арендодателю (хозяину квартиры) арестом?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0102</t>
+  </si>
+  <si>
+    <t>Здравствуйте. Я гражданка России, имею ВНЖ в Казахстане. Может ли моя мама, гражданка РК оформить на меня дарственную на дом ?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0109</t>
+  </si>
+  <si>
+    <t>Здравствуйте, имеет ли военком право блокировать карту каспи во время службы. Ситуация такая что у подруги забрали парня в армию и он ей сказал что военком заблокировал ему карту каспи по причине того что бы на него не взяли кредит и прочий бред, она поверила и дала ему свой счет и карту на которую теперь приходят подозрительные переводы. Она склонна верить ему но я считаю что нет такого что военкомат блокирует карты каспи и что он занимается мошенничеством</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0111</t>
+  </si>
+  <si>
+    <t>здравствуйте. подскажите пожалуйста является ли требование в автобиографии (со стороны кадрового органа войсковых частей) об адресах проживания ближайших родственников нарушением закона о защите персональных данных вышеуказанных родственников? и вообще какие данные на родственников можно указывать в автобиографии при приеме на работу не нарушая данного закона?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0112</t>
+  </si>
+  <si>
+    <t>Здравствуйте меня зовут Андрей. У меня штраф административный по ст. 612ч.3 50 МРП. Управление транспортом ранее лешонным прав. Штраф большой хочу оплатить частями. Как это сделать.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0113</t>
+  </si>
+  <si>
+    <t>Здравствуйте, слова тупорылый, нищеброд и чмошник в личной переписке могут ли попасть под статью 131 УК РК? Истец причем удалил все свои сообщения в самой адрес.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0114</t>
+  </si>
+  <si>
+    <t>Здравствуйте, отправила деньги туроператору, на бронь отелю,оплата прошла онлайн,через 20 минут ,пишет что места в самолёте уже выкуплены,мест нету И теперь не хочет возвращать деньги ,я могу вернуть деньги?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0115</t>
+  </si>
+  <si>
+    <t>Здравствуйте хочу узнать имеет ли банк передавать персональные данные третьим лицам</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0116</t>
+  </si>
+  <si>
+    <t>Здравствуйте! Обязан ли Работодатель выплатить какие-либо компенсационные выплаты работникам, помимо компенсации за неиспользованные дни трудового отпуска и заработной платы, в случае прекращения трудового договора по основанию, предусмотренному пп.1) ст.49 ТК РК - расторжение трудового договора по соглашению сторон?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0117</t>
+  </si>
+  <si>
+    <t>Здравствуйте мне 14 имею ли я право жить у родственников (бабушки и дедушки ) даже если с моими родителями все хорошо</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0118</t>
+  </si>
+  <si>
+    <t>У жены есть сын от первого брака. Ему 13 лет. Мы в браке 3 года, есть общий ребёнок. Сейчас хочу усыновить сына супруги, дать свою фамилию и отчество. От биологического отца разрешение есть. Что нужно для этого? Сын тоже выступает только ЗА эту процедуру со сменой фамилии и отчества.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0122</t>
+  </si>
+  <si>
+    <t>Здравствуйте! Отец является инвалидом II группы в результате исполнения служебных обязанностей во время прохождения воинской службы. Я окончил военную кафедру и зачислен в запас с присвоением офицерского звания. В системе уже присвоили статус военнообязанного. Освобождает ли данный факт меня от призыва на воинскую службу (офицером запаса)?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0123</t>
+  </si>
+  <si>
+    <t>Здравствуйте,подскажите пожалуйста если уволили по статье ,то статья эта имеет срок годности,или она остаётся?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0125</t>
+  </si>
+  <si>
+    <t>Здравствуйте. Можно получить консультацию? Устроилась на работу 1 апреля 4 попала в больницу 3 июня вышла на работу. Работодатель обязан выплатить больничный?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0129</t>
+  </si>
+  <si>
+    <t>Имеет ли право чси взыскать жилье, если оно является единственным и находится в ипотеке?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0133</t>
+  </si>
+  <si>
+    <t>Здравствуйте! Я покупаю автомобиль прежний хозяин умер не возможно переоформить на себя могу ли ездить по страховке?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0134</t>
+  </si>
+  <si>
+    <t>Добрый вечер, сегодня составили договор купля продажи квартир, через отбасы банк ипотеку. Теперь продавец позвонил и говорить если понедельник не получить деньги, то расторгнет договор. В таком случае кто должен оплатить все расходы покупателя которые оплатил за оценку квартир, услуги нотариуса и комиссию отбасы банка</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0136</t>
+  </si>
+  <si>
+    <t>Здравствуйте! У меня вопрос по разделу недвижимости. В разводе 2 года. Подала иск в суд на раздел квартиры, но так как квартира в залоге (ипотека), суд может только определить доли. Ипотека оформлена на бывшего супруга, в квартире проживает он. После определения доли он может требовать с меня половину оплаченной суммы ипотеки? Если еще 10 лет есть, то он остальную часть может просить только после погашения ипотеки или может каждый год подавать в суд, чтобы я платила половину? Я к квартире не имею доступа, тогда я могу с него взять компенсацию за пользование моей долей? Можете объяснить пожалуйста. Заранее спасибо!</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0137</t>
+  </si>
+  <si>
+    <t>Здравствуйте Такой вопрос выложила в сеть скрин переписки моей с мужем? Что за это можно грозить? Вещь есть согласие одного из нас (меня) участника переписки</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0138</t>
+  </si>
+  <si>
+    <t>Я могу направить выписку счетов ответчика, полученных в рамках гражданского дела в афм?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0139</t>
+  </si>
+  <si>
+    <t>Здравствуйте. Я гражданка Баку, Азербайджан. Я столкнулась с мошенничеством со стороны гражданки Алматы. Не зная о том, что она обманным путем присваивает деньги себе, я переводила на карту. Она обещала эти деньги перевести специалисту. Скажите пожалуйста, как мне быть? Я хочу вернуть сумму и добиться ее наказания</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0142</t>
+  </si>
+  <si>
+    <t>Здраствуйте в отношении меня начата исполнительная надпись ,можно узнать что делать в такой ситуации?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0145</t>
+  </si>
+  <si>
+    <t>Здравствуйте. Ситуация: в отношении 12 лет и проживаю в сожительстве с этим мужчиной. Узнала что он поддерживает отношения в форме обычного общения с бывшей женой, детей общих у нех нет. Узнала что она ему написала позно вечером, я прочитала сообщения и ответила ей, с его номера, чтоб она не беспокоила его и не разрушала наши отношения. В ответ на мою просьбу она прислала 36 голосовых сообщений содержащих не цезурные обзывания и оскорбления. Могу ли я написать заявление по статье 131 УК РК, если учесть тот факт, что переписка с этой женщиной велась с номера моего сожителя. Подойдут ли в качестве доказательства голосовые сообщения? Надо ли предупредить обидчицу о своих намерениях, до написания заявления и в какой форме, если она заблокировала все виды связи со мной. Заранее благодарю.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0149</t>
+  </si>
+  <si>
+    <t>Здравствуйте подскажите имеется авьокредитование в евразийском банке. Необходимо ли ежегодно страховать машину именно в каско. И насколько о правомерно.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0151</t>
+  </si>
+  <si>
+    <t>Здравствуйте пожалуйста подскажите Живут мать и сын в арендном жилье 2 ком кв взяли как мать одиночка хотели сделать приватизировать квартиру вопрос сын может ли отказаться от своей доли стороны матери И она будет ли влиять на квадрату квартиры? Или заберут квартиру так как сын отказывается от приватизации</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0152</t>
+  </si>
+  <si>
+    <t>Я продала квартиру 4 года назад. Однако, как оказалось, один из лицевых счетов — за вывоз мусора — до сих пор зарегистрирован на моё имя. Новый собственник накопил долг за мусор, и теперь коммунальное предприятие подало на меня в суд через ЧСИ. Новый владелец платить отказывается, а договор купли-продажи у меня не сохранился. Теперь передо мной стоит вопрос: как я могу доказать, что продала квартиру 4 года назад и не проживаю в ней всё это время? И что это не мой долг.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0153</t>
+  </si>
+  <si>
+    <t>Здравствуйте, я офицер в отставке. 2023 году меня уволили из службы по отрицательным мотивам (отсутствие на службе более 3 часов). В этом году мне выставляют счет за обучение свыше 4 миллионов тенге, хотя мои коллеги которые тоже увольняются из службы возвращают государству до 1 миллиона тенге. Что мне делать подскажите пожалуйста!!! Заранее благодарю.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0155</t>
+  </si>
+  <si>
+    <t>Здравствуйте, подскажите,пожалуйста, я нахожусь в такой жизненной ситуации: молодой человек обещал жениться и создать со мной семью,отговорил от аборта, однако вскоре, не вступив со мной в брак, оставил меня на 2 месяце беременности(сейчас уже 6 месяцев), заблокировал во всех социальных сетях и мой номер телефона, пыталась обратиться к нему по вопросу ухудшения здоровья и угрозы мне и ребенку,безрезультатно. Планирую выйти в декретный отпуск (126 дней). Подскажите, какие пособия я могу оформить, если у нас нет статуса " мать-одиночка"? И как мне подать на установление отцовства с назначением алиментов и ограничением родительских прав,т.к. у отца нет интереса к ребенку, достаточно ли будет скринов переписок для подачи иска в суд?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0156</t>
+  </si>
+  <si>
+    <t>Как можно уволить работника за драку на корпоративе?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0157</t>
+  </si>
+  <si>
+    <t>Здравствуйте. Могут ли наложить арест на недвижимость (1/3 часть), если у мужа долги по кредиту? Недвижимость: это комната в бараке 21 Кв.метр. 1/3 я наследница, а 2/3 сестра.</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0158</t>
+  </si>
+  <si>
+    <t>Здраствуйте, я пенсионерка мне 66, взяла кредит 2 миллиона, проценты 3 на 5 лет, не прочла договор и подписала, сейчас болею и просрочила кредит 1 месяц, что мне делать и как я могу снизить проценты или платить меньше но 10 лет ?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0161</t>
+  </si>
+  <si>
+    <t>Здравствуйте, я работаю на данный момент в компании СОКОЛОВ ювелирный магазин, на должности продавец-кассир 3,5 месяца. Мне 1 мая сообщили о сокращение всей сети и меня это коснулось , предложили сначала два варианта перевод в другой магазин , который мне не удобен , либо увольнение по собственному, родные сказали , чтобы я сказала о увольнение по статье сокращения. Мои работодатели решали этот вопрос 6 дней и пришли к тому , что меня будут оформлять официально в другой ближайший магазин, но работать буду не официально в нынешнем, уже направили мне документы для подписания. Но я беспокоюсь , что в любой им удобный момент, график поставят там где я работать не хочу , что в скорее всего вероятно и не знаю , как мне поступить в такой ситуации, подписывать или нет? Как правильно поступить ?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0162</t>
+  </si>
+  <si>
+    <t>Добрый день! У меня такой вопрос. В прошлом месяце я хотел приобрести новую машину а одном из автосалонов города. Присмотрев одну из них, работники автосалона предложили мне поставить в бронь автомашину, для этого нужно было заплатить сумму в 100тыс.тг. По обстоятельствам у меня не собралась сумма для первоначального взноса, и я решил расторгнуть договор и вернуть уплаченную сумму. Однако менеджер сообщил мне что при расторжении договора уплаченная сумма не возвращается. Хотел узнать законно ли это, т.к. я никаких бумаг что уплачивал сумму не подписывал. Есть лишь квитанция в Каспий что я произвел оплату. Как можно вернуть сумму и что нужно для этого сделать?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0163</t>
+  </si>
+  <si>
+    <t>Здравствуйте, я в начале 2024 года, в трудной ситуации, взяла кредит на 4 млн и отдала своей подруге. Однако, она регулярно задерживает ежемесячные платежи, иногда банк удерживает деньги с моей зарплаты. У нас нет никаких расписок. Она обещает, что вернет деньги в течение двух лет и пишет расписку, но я ей не очень доверяю. Что мне делать в этой ситуации?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0164</t>
+  </si>
+  <si>
+    <t>Могут ли поставить ограничение на счета сожителя, будут ли кредиты считаться личными?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0165</t>
+  </si>
+  <si>
+    <t>Здравствуйте. Был оформлен заказ в каспи магазине у продавца ИП Мадина 21 апреля на сумму 84000тг. В день заказа связались с продавцом уточнить подлинность товара, выяснилось, что товар совсем другой. Более того было предложено нанести логотип/бренд той фирмы , которую мы хотели. Предложили с надписью или нет, всё могут сделать и нарисовать. С тех пор продавец на связь не выходит и товар не отправляет в каспи магазине. Обращались с 21 апреля в чат поддержки каспи магазина, сообщили , что они не могут связаться с продавцом/не выходит на связь , тем самым каждый день говорят : ожидайте. Сегодня 24 апреля вопрос не решён. Каспи магазин ничего не может сделать по отношению к продавцу, а продавец в свою очередь продолжает торговать в этой карточке товара. Переписка с продавцом есть, жду товар чтобы написать претензию. Как решить эту ситуацию? Куда обратиться?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0169</t>
+  </si>
+  <si>
+    <t>Я работаю в частной компании в одной должности, а выполняю фактически обязанности по другой должности без оформления приказа. Моя должность попадает под сокращение штата. Должность с обязанностями, которые я исполняю, не попадает под сокращение штата. Кроме того, в моем отделе имеются вакансии, но их хотят заполнить новыми работниками. Я замечаний и нареканий по работе не имею. Правомерно ли мое сокращение, если аналогичные должности остаются (хотя они будут в новой структуре и их могут переименовать)?</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0170</t>
+  </si>
+  <si>
+    <t>Здравствуйте, имеет ли право сотрудник полиции снимать фиксировать нарушение ПДД на свой личный смартфон или личный телефон? И после предъявлять его в суде в качестве доказательств? Спасибо</t>
+  </si>
+  <si>
+    <t>kz_legalrag_0171</t>
+  </si>
+  <si>
+    <t>Здравствуйте. У папы от первого брака есть дочь. От второго брака двое детей. Мы с братом написали отказ от папиной доли в пользу мамы. Досери от первого брака по наследству достаётся папина доля 1/16, через нотариус уже оформили. У меня такой вопрос: она имеет право жить в квартире с такой долей? Или подарить, продать кому-либо(кроме нас) эту долю? Хотели по-хорошему купить её долю, но человек в обиде на весь мир.</t>
   </si>
 </sst>
 </file>
@@ -414,7 +894,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:D100" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:D101" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="4">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -839,478 +1319,804 @@
       <c r="D21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="C22" s="4"/>
       <c r="D22" s="5"/>
     </row>
     <row r="23">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
+      <c r="A23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="C23" s="8"/>
       <c r="D23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
+      <c r="A24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="C24" s="4"/>
       <c r="D24" s="5"/>
     </row>
     <row r="25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
+      <c r="A25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="C25" s="8"/>
       <c r="D25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="C26" s="4"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="C27" s="8"/>
       <c r="D27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
+      <c r="A28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="C28" s="4"/>
       <c r="D28" s="5"/>
     </row>
     <row r="29">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
+      <c r="A29" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="C29" s="8"/>
       <c r="D29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
+      <c r="A30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C30" s="4"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
+      <c r="A31" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="C31" s="8"/>
       <c r="D31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3"/>
+      <c r="A32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="C32" s="4"/>
       <c r="D32" s="5"/>
     </row>
     <row r="33">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
+      <c r="A33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="C33" s="8"/>
       <c r="D33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3"/>
+      <c r="A34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="C34" s="4"/>
       <c r="D34" s="5"/>
     </row>
     <row r="35">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
+      <c r="A35" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="C35" s="8"/>
       <c r="D35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
+      <c r="A36" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="C36" s="4"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
+      <c r="A37" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="C37" s="8"/>
       <c r="D37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3"/>
+      <c r="A38" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="C38" s="4"/>
       <c r="D38" s="5"/>
     </row>
     <row r="39">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
+      <c r="A39" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="C39" s="8"/>
       <c r="D39" s="9"/>
     </row>
     <row r="40">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3"/>
+      <c r="A40" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="C40" s="4"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7"/>
+      <c r="A41" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>81</v>
+      </c>
       <c r="C41" s="8"/>
       <c r="D41" s="9"/>
     </row>
     <row r="42">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
+      <c r="A42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="C42" s="4"/>
       <c r="D42" s="5"/>
     </row>
     <row r="43">
-      <c r="A43" s="6"/>
-      <c r="B43" s="7"/>
+      <c r="A43" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="C43" s="8"/>
       <c r="D43" s="9"/>
     </row>
     <row r="44">
-      <c r="A44" s="2"/>
-      <c r="B44" s="3"/>
+      <c r="A44" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="C44" s="4"/>
       <c r="D44" s="5"/>
     </row>
     <row r="45">
-      <c r="A45" s="6"/>
-      <c r="B45" s="7"/>
+      <c r="A45" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="C45" s="8"/>
       <c r="D45" s="9"/>
     </row>
     <row r="46">
-      <c r="A46" s="2"/>
-      <c r="B46" s="3"/>
+      <c r="A46" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="C46" s="4"/>
       <c r="D46" s="5"/>
     </row>
     <row r="47">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
+      <c r="A47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="C47" s="8"/>
       <c r="D47" s="9"/>
     </row>
     <row r="48">
-      <c r="A48" s="2"/>
-      <c r="B48" s="3"/>
+      <c r="A48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="C48" s="4"/>
       <c r="D48" s="5"/>
     </row>
     <row r="49">
-      <c r="A49" s="6"/>
-      <c r="B49" s="7"/>
+      <c r="A49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="C49" s="8"/>
       <c r="D49" s="9"/>
     </row>
     <row r="50">
-      <c r="A50" s="2"/>
-      <c r="B50" s="3"/>
+      <c r="A50" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="C50" s="4"/>
       <c r="D50" s="5"/>
     </row>
     <row r="51">
-      <c r="A51" s="6"/>
-      <c r="B51" s="7"/>
+      <c r="A51" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>101</v>
+      </c>
       <c r="C51" s="8"/>
       <c r="D51" s="9"/>
     </row>
     <row r="52">
-      <c r="A52" s="2"/>
-      <c r="B52" s="3"/>
+      <c r="A52" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="C52" s="4"/>
       <c r="D52" s="5"/>
     </row>
     <row r="53">
-      <c r="A53" s="6"/>
-      <c r="B53" s="7"/>
+      <c r="A53" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="C53" s="8"/>
       <c r="D53" s="9"/>
     </row>
     <row r="54">
-      <c r="A54" s="2"/>
-      <c r="B54" s="3"/>
+      <c r="A54" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="C54" s="4"/>
       <c r="D54" s="5"/>
     </row>
     <row r="55">
-      <c r="A55" s="6"/>
-      <c r="B55" s="7"/>
+      <c r="A55" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>109</v>
+      </c>
       <c r="C55" s="8"/>
       <c r="D55" s="9"/>
     </row>
     <row r="56">
-      <c r="A56" s="2"/>
-      <c r="B56" s="3"/>
+      <c r="A56" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="C56" s="4"/>
       <c r="D56" s="5"/>
     </row>
     <row r="57">
-      <c r="A57" s="6"/>
-      <c r="B57" s="7"/>
+      <c r="A57" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>113</v>
+      </c>
       <c r="C57" s="8"/>
       <c r="D57" s="9"/>
     </row>
     <row r="58">
-      <c r="A58" s="2"/>
-      <c r="B58" s="3"/>
+      <c r="A58" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="C58" s="4"/>
       <c r="D58" s="5"/>
     </row>
     <row r="59">
-      <c r="A59" s="6"/>
-      <c r="B59" s="7"/>
+      <c r="A59" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="C59" s="8"/>
       <c r="D59" s="9"/>
     </row>
     <row r="60">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3"/>
+      <c r="A60" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="C60" s="4"/>
       <c r="D60" s="5"/>
     </row>
     <row r="61">
-      <c r="A61" s="6"/>
-      <c r="B61" s="7"/>
+      <c r="A61" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>121</v>
+      </c>
       <c r="C61" s="8"/>
       <c r="D61" s="9"/>
     </row>
     <row r="62">
-      <c r="A62" s="2"/>
-      <c r="B62" s="3"/>
+      <c r="A62" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="C62" s="4"/>
       <c r="D62" s="5"/>
     </row>
     <row r="63">
-      <c r="A63" s="6"/>
-      <c r="B63" s="7"/>
+      <c r="A63" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="C63" s="10"/>
       <c r="D63" s="11"/>
     </row>
     <row r="64">
-      <c r="A64" s="2"/>
-      <c r="B64" s="3"/>
+      <c r="A64" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>127</v>
+      </c>
       <c r="C64" s="10"/>
       <c r="D64" s="11"/>
     </row>
     <row r="65">
-      <c r="A65" s="6"/>
-      <c r="B65" s="7"/>
+      <c r="A65" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>129</v>
+      </c>
       <c r="C65" s="10"/>
       <c r="D65" s="11"/>
     </row>
     <row r="66">
-      <c r="A66" s="2"/>
-      <c r="B66" s="3"/>
+      <c r="A66" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="C66" s="10"/>
       <c r="D66" s="11"/>
     </row>
     <row r="67">
-      <c r="A67" s="6"/>
-      <c r="B67" s="7"/>
+      <c r="A67" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="C67" s="10"/>
       <c r="D67" s="11"/>
     </row>
     <row r="68">
-      <c r="A68" s="2"/>
-      <c r="B68" s="3"/>
+      <c r="A68" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="C68" s="10"/>
       <c r="D68" s="11"/>
     </row>
     <row r="69">
-      <c r="A69" s="6"/>
-      <c r="B69" s="7"/>
+      <c r="A69" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>137</v>
+      </c>
       <c r="C69" s="10"/>
       <c r="D69" s="11"/>
     </row>
     <row r="70">
-      <c r="A70" s="2"/>
-      <c r="B70" s="3"/>
+      <c r="A70" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="C70" s="10"/>
       <c r="D70" s="11"/>
     </row>
     <row r="71">
-      <c r="A71" s="6"/>
-      <c r="B71" s="7"/>
+      <c r="A71" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>141</v>
+      </c>
       <c r="C71" s="10"/>
       <c r="D71" s="11"/>
     </row>
     <row r="72">
-      <c r="A72" s="2"/>
-      <c r="B72" s="3"/>
+      <c r="A72" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="C72" s="10"/>
       <c r="D72" s="11"/>
     </row>
     <row r="73">
-      <c r="A73" s="6"/>
-      <c r="B73" s="7"/>
+      <c r="A73" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>145</v>
+      </c>
       <c r="C73" s="10"/>
       <c r="D73" s="11"/>
     </row>
     <row r="74">
-      <c r="A74" s="2"/>
-      <c r="B74" s="3"/>
+      <c r="A74" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="C74" s="10"/>
       <c r="D74" s="11"/>
     </row>
     <row r="75">
-      <c r="A75" s="6"/>
-      <c r="B75" s="7"/>
+      <c r="A75" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>149</v>
+      </c>
       <c r="C75" s="10"/>
       <c r="D75" s="11"/>
     </row>
     <row r="76">
-      <c r="A76" s="2"/>
-      <c r="B76" s="3"/>
+      <c r="A76" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="C76" s="10"/>
       <c r="D76" s="11"/>
     </row>
     <row r="77">
-      <c r="A77" s="6"/>
-      <c r="B77" s="7"/>
+      <c r="A77" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>153</v>
+      </c>
       <c r="C77" s="10"/>
       <c r="D77" s="11"/>
     </row>
     <row r="78">
-      <c r="A78" s="2"/>
-      <c r="B78" s="3"/>
+      <c r="A78" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="C78" s="10"/>
       <c r="D78" s="11"/>
     </row>
     <row r="79">
-      <c r="A79" s="6"/>
-      <c r="B79" s="7"/>
+      <c r="A79" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>157</v>
+      </c>
       <c r="C79" s="10"/>
       <c r="D79" s="11"/>
     </row>
     <row r="80">
-      <c r="A80" s="2"/>
-      <c r="B80" s="3"/>
+      <c r="A80" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="C80" s="10"/>
       <c r="D80" s="11"/>
     </row>
     <row r="81">
-      <c r="A81" s="6"/>
-      <c r="B81" s="7"/>
+      <c r="A81" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>161</v>
+      </c>
       <c r="C81" s="10"/>
       <c r="D81" s="11"/>
     </row>
     <row r="82">
-      <c r="A82" s="2"/>
-      <c r="B82" s="3"/>
+      <c r="A82" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>163</v>
+      </c>
       <c r="C82" s="10"/>
       <c r="D82" s="11"/>
     </row>
     <row r="83">
-      <c r="A83" s="6"/>
-      <c r="B83" s="7"/>
+      <c r="A83" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="C83" s="10"/>
       <c r="D83" s="11"/>
     </row>
     <row r="84">
-      <c r="A84" s="2"/>
-      <c r="B84" s="3"/>
+      <c r="A84" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="C84" s="10"/>
       <c r="D84" s="11"/>
     </row>
     <row r="85">
-      <c r="A85" s="6"/>
-      <c r="B85" s="7"/>
+      <c r="A85" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>169</v>
+      </c>
       <c r="C85" s="10"/>
       <c r="D85" s="11"/>
     </row>
     <row r="86">
-      <c r="A86" s="2"/>
-      <c r="B86" s="3"/>
+      <c r="A86" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="C86" s="10"/>
       <c r="D86" s="11"/>
     </row>
     <row r="87">
-      <c r="A87" s="6"/>
-      <c r="B87" s="7"/>
+      <c r="A87" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>173</v>
+      </c>
       <c r="C87" s="10"/>
       <c r="D87" s="11"/>
     </row>
     <row r="88">
-      <c r="A88" s="2"/>
-      <c r="B88" s="3"/>
+      <c r="A88" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="C88" s="10"/>
       <c r="D88" s="11"/>
     </row>
     <row r="89">
-      <c r="A89" s="6"/>
-      <c r="B89" s="7"/>
+      <c r="A89" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>177</v>
+      </c>
       <c r="C89" s="10"/>
       <c r="D89" s="11"/>
     </row>
     <row r="90">
-      <c r="A90" s="2"/>
-      <c r="B90" s="3"/>
+      <c r="A90" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>179</v>
+      </c>
       <c r="C90" s="10"/>
       <c r="D90" s="11"/>
     </row>
     <row r="91">
-      <c r="A91" s="6"/>
-      <c r="B91" s="7"/>
+      <c r="A91" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>181</v>
+      </c>
       <c r="C91" s="10"/>
       <c r="D91" s="11"/>
     </row>
     <row r="92">
-      <c r="A92" s="2"/>
-      <c r="B92" s="3"/>
+      <c r="A92" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="C92" s="10"/>
       <c r="D92" s="11"/>
     </row>
     <row r="93">
-      <c r="A93" s="6"/>
-      <c r="B93" s="7"/>
+      <c r="A93" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>185</v>
+      </c>
       <c r="C93" s="10"/>
       <c r="D93" s="11"/>
     </row>
     <row r="94">
-      <c r="A94" s="2"/>
-      <c r="B94" s="3"/>
+      <c r="A94" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="C94" s="10"/>
       <c r="D94" s="11"/>
     </row>
     <row r="95">
-      <c r="A95" s="6"/>
-      <c r="B95" s="7"/>
+      <c r="A95" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>189</v>
+      </c>
       <c r="C95" s="10"/>
       <c r="D95" s="11"/>
     </row>
     <row r="96">
-      <c r="A96" s="2"/>
-      <c r="B96" s="3"/>
+      <c r="A96" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="C96" s="10"/>
       <c r="D96" s="11"/>
     </row>
     <row r="97">
-      <c r="A97" s="6"/>
-      <c r="B97" s="7"/>
+      <c r="A97" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>193</v>
+      </c>
       <c r="C97" s="10"/>
       <c r="D97" s="11"/>
     </row>
     <row r="98">
-      <c r="A98" s="2"/>
-      <c r="B98" s="3"/>
+      <c r="A98" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="C98" s="10"/>
       <c r="D98" s="11"/>
     </row>
     <row r="99">
-      <c r="A99" s="6"/>
-      <c r="B99" s="7"/>
+      <c r="A99" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>197</v>
+      </c>
       <c r="C99" s="10"/>
       <c r="D99" s="11"/>
     </row>
     <row r="100">
-      <c r="A100" s="2"/>
-      <c r="B100" s="3"/>
+      <c r="A100" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>199</v>
+      </c>
       <c r="C100" s="10"/>
       <c r="D100" s="11"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C101" s="10"/>
+      <c r="D101" s="11"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
